--- a/entertainment_forms/017_virtual_trick_or_treat_party_registration_form--entertainment_forms.xlsx
+++ b/entertainment_forms/017_virtual_trick_or_treat_party_registration_form--entertainment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Party Details</t>
+          <t>What is your party name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,70 +577,70 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>party_details</t>
+          <t>trick_treat_preferences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Party Details</t>
+          <t>Do you want a treat or just attend the party?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>trick_treat_preferences</t>
+          <t>stay_time</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Trick or Treat Preferences</t>
+          <t>How long do you want to stay for the party?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>trick_treat_preferences</t>
+          <t>favorite_halloween_character</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Trick or Treat</t>
+          <t>What is your favorite Halloween character?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rsvp</t>
+          <t>dietary_restrictions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RSVP</t>
+          <t>Do you have any dietary restrictions?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>party_details</t>
+          <t>guest_count</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Party Details</t>
+          <t>How many guests are you bringing?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>party_details</t>
+          <t>favorite_halloween_candy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Party Details</t>
+          <t>What is your favorite Halloween candy?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>trick_treat_preferences</t>
+          <t>trick_treat</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Trick or Treat</t>
+          <t>Do you like treats?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>party_details</t>
+          <t>trick_treat_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Party Details</t>
+          <t>Trick or Treat</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>trick_treat_preferences</t>
+          <t>trick_treat_preferences_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Trick or Treat</t>
+          <t>Trick or Treat preferences</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -895,100 +895,287 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>favorite_halloween_character_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>witch</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Witch</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>favorite_halloween_character_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>ghost</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Ghost</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>favorite_halloween_character_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>monster</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Monster</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>favorite_halloween_character_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>vampire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vampire</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>trick_treat_preferences_choices</t>
+          <t>dietary_restrictions_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>dietary_restrictions_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>yes,_with_advance_notice</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Yes, with advance notice</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>favorite_halloween_candy_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>candy</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Candy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>favorite_halloween_candy_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>chocolates</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Chocolates</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>favorite_halloween_candy_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>lollipops</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Lollipops</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>favorite_halloween_candy_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sweets</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sweets</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>trick_treat_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>trick_treat_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>trick_treat_2_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>trick_treat_2_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>trick_treat_preferences_2_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>trick_treat_preferences_2_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
